--- a/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
+++ b/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>**STI-103 — Logika Informatika** (*Informatics Logic*)</t>
+          <t>**STI-103 — Arsitektur dan Organisasi Sistem Teknologi Informasi** (*Architecture and Organization of Information Technology Systems*)</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>**Semester 1** / Komputasi Cerdas &amp; Teori Bahasa (Core STI)</t>
+          <t>**Semester 1** / Infrastruktur, Sistem &amp; Komputasi Awan (Core STI)</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>Tidak Ada</t>
+          <t>Tidak Ada (Fondasi Sistem Tingkat Pertama)</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>`P1` (Fondasi Logika Komputasi), `KU1` (Penalaran Formal Kritis)</t>
+          <t>`P1` (Representasi Data Biner &amp; Logika), `P3` (Arsitektur Perangkat Keras, Virtualisasi &amp; Infrastruktur TI), `KU1` (Pemikiran Logis Rekayasa Sistem)</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>`PL-1`, `PL-2`</t>
+          <t>`PL-1` (Intelligent IS &amp; AI Engineer), `PL-2` (Cloud Infrastructure &amp; Cybersecurity Integrator)</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>`PEO-1` (Professional Practice), `PEO-3` (Research)</t>
+          <t>`PEO-1` (Professional Practice &amp; Systems Integration), `PEO-3` (Research &amp; Lifelong Learning)</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>Mahasiswa (*A*) mampu **mengonstruksi** tabel kebenaran dan ekuivalensi logika proposisi (*B*) dari pernyataan bahasa alami (*C*) secara akurat dan konsisten (*D*).</t>
+          <t>Mahasiswa (*A*) mampu **menerapkan** representasi data biner, heksadesimal, floating point IEEE 754, dan siklus eksekusi instruksi Von Neumann (*B*) pada arsitektur prosesor (*C*) secara tepat dan akurat (*D*).</t>
         </is>
       </c>
       <c r="C167" s="8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>`P1`</t>
+          <t>`P1, P3`</t>
         </is>
       </c>
     </row>
@@ -3750,17 +3750,17 @@
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>Mahasiswa (*A*) mampu **mentransformasikan** formula logika ke bentuk normal standar CNF dan DNF (*B*) menggunakan hukum-hukum logika formal (*C*) dengan struktur klausa yang valid (*D*).</t>
+          <t>Mahasiswa (*A*) mampu **menganalisis** rancangan rangkaian logika kombinasional dan sekuensial (*B*) menggunakan gerbang logika biner dan flip-flop (*C*) sebagai dasar operasi Arithmetic Logic Unit (ALU) (*D*).</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>**C3**</t>
-        </is>
-      </c>
-      <c r="D168" s="10" t="inlineStr">
-        <is>
-          <t>`P1`</t>
+          <t>**C4**</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>`P1, KU1`</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>Mahasiswa (*A*) mampu **merumuskan** ekspresi logika predikat orde pertama (FOL) dengan kuantor universal dan eksistensial (*B*) pada domain relasi objek kompleks (*C*) secara tepat (*D*).</t>
+          <t>Mahasiswa (*A*) mampu **membandingkan** karakteristik arsitektur prosesor CISC (x86_64) vs RISC (ARM64 / RISC-V), hirarki memori cache L1/L2/L3, dan akselerator komputasi GPU/NPU (*B*) dalam skenario beban kerja komputasi nyata (*C*) secara kritis (*D*).</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>`P1, KU1`</t>
+          <t>`P3, KU1`</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>Mahasiswa (*A*) mampu **membuktikan** validitas argumen inferensi (*B*) menggunakan metode Resolusi dan aturan inferensi formal (*C*) sebagai landasan sistem penalaran AI (*D*).</t>
+          <t>Mahasiswa (*A*) mampu **mengevaluasi** mekanisme bus sistem, interupsi I/O, abstraksi virtualisasi hardware (Hypervisor), dan organisasi server data center (*B*) untuk mendukung infrastruktur cloud modern (*C*) secara komprehensif (*D*).</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
@@ -3802,9 +3802,9 @@
           <t>**C5**</t>
         </is>
       </c>
-      <c r="D170" s="10" t="inlineStr">
-        <is>
-          <t>`KU1`</t>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>`P3, KU1`</t>
         </is>
       </c>
     </row>
@@ -3856,17 +3856,17 @@
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>Mampu membedakan proposisi, nilai kebenaran, operator dasar (C2)</t>
+          <t>Mampu menguraikan model Von Neumann dan evolusi arsitektur komputer (C2)</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>Pengantar Logika Matematika, Proposisi Atomik &amp; Majemuk</t>
+          <t>Arsitektur Komputer Modern, Model Von Neumann, dan Komponen Utama</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>Kuliah &amp; Latihan (150m)</t>
+          <t>Kuliah &amp; Diskusi (150m)</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>Mampu menyusun tabel kebenaran proposisi majemuk &amp; tautologi (C3)</t>
+          <t>Mampu mengonversi bilangan biner, oktal, heksadesimal, dan komplemen dua (C3)</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>Tabel Kebenaran, Tautologi, Kontradiksi, Kontingensi</t>
+          <t>Representasi Data Komputasi: Integer Biner, Two's Complement</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>Mampu membuktikan ekuivalensi logis dengan hukum-hukum logika (C3)</t>
+          <t>Mampu menghitung representasi floating point standar IEEE 754 (C3)</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>Hukum Aljabar Proposisi dan Ekuivalensi Logis</t>
+          <t>Format Floating Point IEEE 754 (Single &amp; Double Precision)</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
@@ -3937,22 +3937,22 @@
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>**Mampu mengonversi formula logika ke bentuk CNF dan DNF (C3)**</t>
+          <t>**Mampu merancang rangkaian logika kombinasional ALU dasar (C4)**</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
         <is>
-          <t>**Bentuk Normal Konjungtif (CNF) &amp; Disjungtif (DNF)**</t>
+          <t>**Gerbang Logika, Half/Full Adder, Multiplexer, dan Decoder**</t>
         </is>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>**Problem-Solving (150m)**</t>
+          <t>**Problem-Based (150m)**</t>
         </is>
       </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
-          <t>**Tugas 1: Kuis &amp; Problem Solving (Bobot: 20%)**</t>
+          <t>**Tugas 1: Kuis &amp; Problem Solving Logika Biner (Bobot: 20%)**</t>
         </is>
       </c>
     </row>
@@ -3964,17 +3964,17 @@
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Mampu menerapkan aturan inferensi Modus Ponens &amp; Tollens (C3)</t>
+          <t>Mampu menganalisis rangkaian sekuensial, flip-flop, dan register (C4)</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>Aturan Inferensi: Modus Ponens, Tollens, Silogisme</t>
+          <t>Rangkaian Sekuensial: RS, D, JK Flip-Flop, Register, Counter</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Kuliah &amp; Diskusi (150m)</t>
+          <t>Kuliah &amp; Latihan (150m)</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>Mampu membuktikan validitas argumen via tabel &amp; pohon semantik (C4)</t>
+          <t>Mampu menguraikan struktur internal CPU (ALU, Control Unit, Register Set) (C2)</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
         <is>
-          <t>Pembuktian Validitas Argumen Proposisional</t>
+          <t>Organisasi Prosesor: Datapath, Control Unit, dan Register Bank</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>Problem-Based Class (150m)</t>
+          <t>Problem-Solving Class (150m)</t>
         </is>
       </c>
       <c r="E179" s="9" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>Mampu menerapkan metode Resolusi Proposisional (C4)</t>
+          <t>Mampu menganalisis siklus instruksi Fetch-Decode-Execute dan Addressing Modes (C4)</t>
         </is>
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>Prinsip Resolusi, Klausa Horn, dan Refutation Proof</t>
+          <t>Siklus Instruksi Mesin, Mode Pengalamatan, dan Format Instruksi</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C181" s="9" t="inlineStr">
         <is>
-          <t>**Ujian Tertulis Logika Proposisi, CNF/DNF, &amp; Resolusi Dasar**</t>
+          <t>**Ujian Tertulis Representasi Biner, Logika Digital, &amp; Datapath CPU**</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t>Mampu menguraikan predikat, term, fungsi, dan semesta wacana (C2)</t>
+          <t>Mampu membedakan arsitektur instruksi CISC (x86) vs RISC (ARM64 / RISC-V) (C4)</t>
         </is>
       </c>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>Logika Predikat Orde Pertama (First-Order Logic / FOL)</t>
+          <t>Arsitektur Set Instruksi: CISC vs RISC, Karakteristik ARM64 &amp; RISC-V</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>Kuliah &amp; Latihan (150m)</t>
+          <t>Kuliah Interaktif (150m)</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>Mampu merumuskan kuantor Universal dan Eksistensial (C3)</t>
+          <t>Mampu menganalisis prinsip kerja Pipelining instruksi dan hazard (C4)</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
         <is>
-          <t>Kuantor Tunggal, Negasi Kuantor, dan Translasi Kalimat</t>
+          <t>Instruksi Pipelining, Data Hazard, Control Hazard, Branch Prediction</t>
         </is>
       </c>
       <c r="D183" s="9" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>Mampu menganalisis kuantor bertingkat (Nested Quantifiers) (C4)</t>
+          <t>Mampu mengevaluasi hirarki memori, prinsip lokalitas, dan Cache L1/L2/L3 (C4)</t>
         </is>
       </c>
       <c r="C184" s="7" t="inlineStr">
         <is>
-          <t>Kuantor Jamak dan Interpretasi Domain Relasi</t>
+          <t>Hirarki Memori: Cache Mapping (Direct, Associative), Hit/Miss Ratio</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
@@ -4153,22 +4153,22 @@
       </c>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>**Mampu mengubah formula FOL ke Bentuk Klausa Standar (C3)**</t>
+          <t>**Mampu menganalisis arsitektur akselerator paralel GPU &amp; NPU untuk AI (C4)**</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>**Skolemization dan Prenex Normal Form (PNF)**</t>
+          <t>**Komputasi Paralel: Perbedaan CPU Multicore vs GPU Tensor Cores vs NPU**</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>**Kuliah &amp; Latihan Soal (150m)**</t>
+          <t>**Kuliah &amp; Analisis Kasus (150m)**</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>**Tugas 2: Studi Kasus / Paper Analisis (Bobot: 20%)**</t>
+          <t>**Tugas 2: Studi Kasus Arsitektur Hardware AI &amp; Server (Bobot: 20%)**</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>Mampu melakukan proses Unifikasi pada logika predikat (C4)</t>
+          <t>Mampu menganalisis memori utama (RAM DDR4/DDR5) dan Virtual Memory (C4)</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>Algoritma Unifikasi dan Most General Unifier (MGU)</t>
+          <t>Memori Utama, Paging, Page Table, dan Memory Management Unit (MMU)</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>Mampu membuktikan teorema dengan Resolusi FOL (C5)</t>
+          <t>Mampu menguraikan sistem I/O, Bus standar (PCIe, NVMe), dan Interrupt Handling (C3)</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
         <is>
-          <t>Resolusi pada Logika Predikat dan Refutation Tree</t>
+          <t>Subistem I/O: Programmed I/O, Interrupt-Driven I/O, Direct Memory Access (DMA)</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
@@ -4234,17 +4234,17 @@
       </c>
       <c r="B188" s="7" t="inlineStr">
         <is>
-          <t>Mampu memodelkan rule base pada basis penalaran AI Prolog (C4)</t>
+          <t>Mampu mengevaluasi virtualisasi hardware (Intel VT-x) &amp; arsitektur server data center (C5)</t>
         </is>
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>Pemrograman Logika: Pengantar Prolog Syntax &amp; Query</t>
+          <t>Virtualisasi Perangkat Keras, Hypervisor Type 1/2, Arsitektur Server Cloud</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Demo &amp; Lab Komputasi (150m)</t>
+          <t>Demo &amp; Studi Kasus (150m)</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="C189" s="9" t="inlineStr">
         <is>
-          <t>**Ujian Komprehensif Logika Predikat, Unifikasi, &amp; Resolusi FOL**</t>
+          <t>**Ujian Komprehensif Arsitektur Prosesor, Cache, GPU AI, &amp; Virtualisasi**</t>
         </is>
       </c>
       <c r="D189" s="9" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="B296" s="7" t="inlineStr">
         <is>
-          <t>**STI-201 — Matematika Diskrit** (*Discrete Mathematics*)</t>
+          <t>**STI-201 — Matematika Diskrit dan Logika** (*Discrete Mathematics and Logic*)</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B299" s="9" t="inlineStr">
         <is>
-          <t>`STI-103` Logika Informatika</t>
+          <t>`STI-103` Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B300" s="7" t="inlineStr">
         <is>
-          <t>`P1` (Fondasi Struktur Diskrit, Teori Graf &amp; Komputasi)</t>
+          <t>`P1` (Fondasi Struktur Diskrit, Logika Komputasi &amp; Graf), `KU1` (Penalaran Formal Kritis)</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B302" s="7" t="inlineStr">
         <is>
-          <t>`PEO-1` (Professional Practice), `PEO-3` (Research)</t>
+          <t>`PEO-1` (Professional Practice), `PEO-3` (Research &amp; Lifelong Learning)</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="B306" s="7" t="inlineStr">
         <is>
-          <t>Mahasiswa (*A*) mampu **membuktikan** pernyataan matematika dan kebenaran algoritma (*B*) menggunakan metode induksi matematika (*C*) dengan runtutan formal yang valid (*D*).</t>
+          <t>Mahasiswa (*A*) mampu **membuktikan** validitas argumen inferensi logika proposisi/predikat dan kebenaran algoritma (*B*) menggunakan tabel kebenaran, hukum aljabar logika, dan metode induksi matematika (*C*) secara runtut dan valid (*D*).</t>
         </is>
       </c>
       <c r="C306" s="8" t="inlineStr">
@@ -6442,9 +6442,9 @@
           <t>**C3**</t>
         </is>
       </c>
-      <c r="D306" s="8" t="inlineStr">
-        <is>
-          <t>`P1`</t>
+      <c r="D306" s="7" t="inlineStr">
+        <is>
+          <t>`P1, KU1`</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B307" s="9" t="inlineStr">
         <is>
-          <t>Mahasiswa (*A*) mampu **menerapkan** konsep relasi ekuivalensi, himpunan terurut parsial (Poset), dan kombinatorika (*B*) pada pemodelan struktur data komputasi (*C*) secara tepat (*D*).</t>
+          <t>Mahasiswa (*A*) mampu **menerapkan** konsep relasi ekuivalensi, himpunan terurut parsial (Poset), aljabar Boolean, dan kombinatorika (*B*) pada pemodelan struktur data dan logika query basis data (*C*) secara tepat (*D*).</t>
         </is>
       </c>
       <c r="C307" s="10" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="B308" s="7" t="inlineStr">
         <is>
-          <t>Mahasiswa (*A*) mampu **menganalisis** struktur Graf dan Pohon (Tree) (*B*) menggunakan matriks representasi dan algoritma penelusuran lintasan (*C*) untuk optimasi jaringan komputer/data (*D*).</t>
+          <t>Mahasiswa (*A*) mampu **menganalisis** struktur Graf dan Pohon (Tree) (*B*) menggunakan matriks representasi (Adjacency Matrix) dan algoritma penelusuran lintasan (*C*) untuk optimasi jaringan data/komputer (*D*).</t>
         </is>
       </c>
       <c r="C308" s="8" t="inlineStr">
@@ -6486,9 +6486,9 @@
           <t>**C4**</t>
         </is>
       </c>
-      <c r="D308" s="8" t="inlineStr">
-        <is>
-          <t>`P1`</t>
+      <c r="D308" s="7" t="inlineStr">
+        <is>
+          <t>`P1, KU1`</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="B309" s="9" t="inlineStr">
         <is>
-          <t>Mahasiswa (*A*) mampu **mengonstruksi** model otomata berhingga (Finite State Automata / FSA) (*B*) untuk pengenalan pola bahasa formal dan transisi status sistem (*C*) secara akurat (*D*).</t>
+          <t>Mahasiswa (*A*) mampu **mengonstruksi** model otomata berhingga (Finite State Automata / FSA: DFA dan NFA) (*B*) untuk pengenalan pola bahasa formal dan transisi status sistem komputasi (*C*) secara akurat (*D*).</t>
         </is>
       </c>
       <c r="C309" s="10" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B313" s="7" t="inlineStr">
         <is>
-          <t>Mampu mengoperasikan aljabar himpunan dan hukum himpunan (C3)</t>
+          <t>Mampu memformulasikan logika proposisi, tabel kebenaran, dan ekuivalensi (C3)</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
         <is>
-          <t>Teori Himpunan Lanjut, Operasi Biner, Diagram Venn</t>
+          <t>Logika Proposisional, Tabel Kebenaran, Tautologi, Hukum Logika</t>
         </is>
       </c>
       <c r="D313" s="7" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="B314" s="9" t="inlineStr">
         <is>
-          <t>Mampu menganalisis relasi biner, matriks relasi, relasi ekuivalen (C4)</t>
+          <t>Mampu menganalisis logika predikat, kuantor universal &amp; eksistensial (C4)</t>
         </is>
       </c>
       <c r="C314" s="9" t="inlineStr">
         <is>
-          <t>Relasi Biner, Sifat Relasi, dan Partisi Himpunan</t>
+          <t>Logika Predikat Orde Pertama (FOL) dan Kuantor Logika</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="B315" s="7" t="inlineStr">
         <is>
-          <t>Mampu membedakan fungsi injektif, surjektif, bijektif, dan invers (C2)</t>
+          <t>Mampu membuktikan validitas argumen via Modus Ponens/Tollens &amp; Resolusi (C4)</t>
         </is>
       </c>
       <c r="C315" s="7" t="inlineStr">
         <is>
-          <t>Teori Fungsi Matematika dan Komposisi Fungsi</t>
+          <t>Aturan Inferensi Formal dan Prinsip Resolusi Logika</t>
         </is>
       </c>
       <c r="D315" s="7" t="inlineStr">
         <is>
-          <t>Ceramah &amp; Latihan (150m)</t>
+          <t>Case-Based Learning (150m)</t>
         </is>
       </c>
       <c r="E315" s="7" t="inlineStr">
@@ -6648,17 +6648,17 @@
       </c>
       <c r="C316" s="9" t="inlineStr">
         <is>
-          <t>**Induksi Matematika dan Program Correctness**</t>
+          <t>**Induksi Matematika dan Verifikasi Kebenaran Algoritma**</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>**Problem-Based Learning (150m)**</t>
+          <t>**Problem-Based (150m)**</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>**Tugas 1: Kuis &amp; Problem Solving (Bobot: 20%)**</t>
+          <t>**Tugas 1: Kuis &amp; Problem Solving Logika/Induksi (Bobot: 20%)**</t>
         </is>
       </c>
     </row>
@@ -6670,12 +6670,12 @@
       </c>
       <c r="B317" s="7" t="inlineStr">
         <is>
-          <t>Mampu menghitung permutasi, kombinasi, dan kaidah pencacahan (C3)</t>
+          <t>Mampu mengoperasikan aljabar himpunan, relasi biner, dan fungsi (C3)</t>
         </is>
       </c>
       <c r="C317" s="7" t="inlineStr">
         <is>
-          <t>Kombinatorika Dasar: Kaidah Penjumlahan &amp; Perkalian</t>
+          <t>Teori Himpunan, Relasi Ekuivalensi, Partisi, dan Sifat Fungsi</t>
         </is>
       </c>
       <c r="D317" s="7" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="B318" s="9" t="inlineStr">
         <is>
-          <t>Mampu menerapkan Prinsip Sarang Merpati &amp; Teorema Binomial (C3)</t>
+          <t>Mampu menghitung permutasi, kombinasi, dan kaidah pencacahan (C3)</t>
         </is>
       </c>
       <c r="C318" s="9" t="inlineStr">
         <is>
-          <t>Pigeonhole Principle dan Koefisien Binomial</t>
+          <t>Kombinatorika Dasar: Kaidah Penjumlahan, Perkalian, Pigeonhole</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="C320" s="9" t="inlineStr">
         <is>
-          <t>**Ujian Tertulis Himpunan, Relasi, Induksi, &amp; Kombinatorika**</t>
+          <t>**Ujian Tertulis Logika Formal, Induksi, Relasi, &amp; Kombinatorika**</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="B321" s="7" t="inlineStr">
         <is>
-          <t>Mampu mengidentifikasi terminologi graf dan graf khusus (C2)</t>
+          <t>Mampu mengidentifikasi terminologi graf, derajat simpul, graf isomorfik (C2)</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
         <is>
-          <t>Pengantar Teori Graf: Derajat Simpul, Graf Isomorfik</t>
+          <t>Pengantar Teori Graf, Graf Sederhana, Graf Bipartit</t>
         </is>
       </c>
       <c r="D321" s="7" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="B322" s="9" t="inlineStr">
         <is>
-          <t>Mampu merepresentasikan graf via Adjacency Matrix &amp; List (C3)</t>
+          <t>Mampu merepresentasikan graf via Adjacency Matrix &amp; Adjacency List (C3)</t>
         </is>
       </c>
       <c r="C322" s="9" t="inlineStr">
         <is>
-          <t>Representasi Graf dalam Memori Komputer</t>
+          <t>Representasi Graf dalam Memori Komputer &amp; Algoritma Traversal</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>**Tugas 2: Studi Kasus / Paper Analisis (Bobot: 20%)**</t>
+          <t>**Tugas 2: Studi Kasus Pemodelan Graf Jaringan (Bobot: 20%)**</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="B326" s="9" t="inlineStr">
         <is>
-          <t>Mampu menerapkan Pewarnaan Graf (Graph Coloring) (C4)</t>
+          <t>Mampu menerapkan Pewarnaan Graf (Graph Coloring) pada penjadwalan (C4)</t>
         </is>
       </c>
       <c r="C326" s="9" t="inlineStr">
         <is>
-          <t>Pewarnaan Graf, Bilangan Kromatik, dan Alokasi Register</t>
+          <t>Pewarnaan Graf, Bilangan Kromatik, dan Alokasi Register/Jadwal</t>
         </is>
       </c>
       <c r="D326" s="9" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="B620" s="9" t="inlineStr">
         <is>
-          <t>`STI-103` Logika Informatika</t>
+          <t>`STI-201` Matematika Diskrit dan Logika, `FST-204` Pengantar AI &amp; Data</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
+++ b/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
@@ -24479,7 +24479,7 @@
       </c>
       <c r="B1227" s="9" t="inlineStr">
         <is>
-          <t>`STI-205` Pemrograman Lanjut &amp; `STI-306` Web Frontend</t>
+          <t>`FST-203` Struktur Data &amp; Algoritma, `STI-306` Web Front End Development</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
+++ b/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
@@ -557,7 +557,7 @@
     <col width="69" customWidth="1" min="1" max="1"/>
     <col width="69" customWidth="1" min="2" max="2"/>
     <col width="69" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="47.15" customWidth="1" min="4" max="4"/>
     <col width="69" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
@@ -27227,7 +27227,7 @@
       </c>
       <c r="B1367" s="9" t="inlineStr">
         <is>
-          <t>**3 SKS** / Tipe: **+P** (100m Teori + 170m Lab + 180m Mandiri)</t>
+          <t>**2 SKS** / Tipe: **Teori** (100m Kuliah + 120m Mandiri)</t>
         </is>
       </c>
     </row>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="B1369" s="9" t="inlineStr">
         <is>
-          <t>`STI-101` Pengantar Sistem &amp; TI</t>
+          <t>`STI-521` Internet of Things (IoT)</t>
         </is>
       </c>
     </row>
@@ -27656,17 +27656,17 @@
       </c>
       <c r="C1390" s="9" t="inlineStr">
         <is>
-          <t>**Ujian Analisis Domain SPBE &amp; Koding Pemetaan Spasial Web GIS**</t>
+          <t>**Ujian Analisis Domain SPBE &amp; Arsitektur Layanan Smart City**</t>
         </is>
       </c>
       <c r="D1390" s="9" t="inlineStr">
         <is>
-          <t>**Ujian Tertulis &amp; Lab (170m)**</t>
+          <t>**Ujian Tertulis / Case Analysis (100m)**</t>
         </is>
       </c>
       <c r="E1390" s="9" t="inlineStr">
         <is>
-          <t>**UTS: Evaluasi Proyek Awal 50% / Ujian Praktik (Bobot: 25%)**</t>
+          <t>**UTS: Ujian Tertulis Teori (Bobot: 30%)**</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
+++ b/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
@@ -650,12 +650,12 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>14 MK</t>
+          <t>13 MK</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>38 SKS</t>
+          <t>36 SKS</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>27 MK</t>
+          <t>28 MK</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>77 SKS</t>
+          <t>79 SKS</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -33485,7 +33485,7 @@
       </c>
       <c r="B1687" s="7" t="inlineStr">
         <is>
-          <t>**STA-01 — Decision Support Systems** (*Decision Support Systems*)</t>
+          <t>**STA-501 — Decision Support Systems** (*Decision Support Systems*)</t>
         </is>
       </c>
     </row>
@@ -34167,7 +34167,7 @@
       </c>
       <c r="B1722" s="7" t="inlineStr">
         <is>
-          <t>**STA-02 — Computational Methods and Numerics** (*Computational Methods and Numerics*)</t>
+          <t>**STA-601 — Computational Methods and Numerics** (*Computational Methods and Numerics*)</t>
         </is>
       </c>
     </row>
@@ -34871,7 +34871,7 @@
       </c>
       <c r="B1758" s="7" t="inlineStr">
         <is>
-          <t>**STA-03 — Intelligent Agent Systems** (*Intelligent Agent Systems*)</t>
+          <t>**STA-602 — Intelligent Agent Systems** (*Intelligent Agent Systems*)</t>
         </is>
       </c>
     </row>
@@ -35575,7 +35575,7 @@
       </c>
       <c r="B1794" s="7" t="inlineStr">
         <is>
-          <t>**STA-04 — MLOps and AI Pipeline** (*MLOps and AI Pipeline*)</t>
+          <t>**STA-701 — MLOps and AI Pipeline** (*MLOps and AI Pipeline*)</t>
         </is>
       </c>
     </row>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="B1829" s="7" t="inlineStr">
         <is>
-          <t>**STA-05 — Conversational AI and Intelligent Assistant** (*Conversational AI &amp; Intelligent Assistant*)</t>
+          <t>**STA-702 — Conversational AI and Intelligent Assistant** (*Conversational AI &amp; Intelligent Assistant*)</t>
         </is>
       </c>
     </row>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="B1865" s="7" t="inlineStr">
         <is>
-          <t>**STA-06 — Smart Surveillance and IoT Analytics** (*Smart Surveillance and IoT Analytics*)</t>
+          <t>**STA-703 — Smart Surveillance and IoT Analytics** (*Smart Surveillance and IoT Analytics*)</t>
         </is>
       </c>
     </row>
@@ -37665,7 +37665,7 @@
       </c>
       <c r="B1901" s="7" t="inlineStr">
         <is>
-          <t>**STB-01 — Network Security and Digital Forensics** (*Network Security and Digital Forensics*)</t>
+          <t>**STB-501 — Network Security and Digital Forensics** (*Network Security and Digital Forensics*)</t>
         </is>
       </c>
     </row>
@@ -38347,7 +38347,7 @@
       </c>
       <c r="B1936" s="7" t="inlineStr">
         <is>
-          <t>**STB-02 — Cloud Architecture &amp; DevOps** (*Cloud Architecture &amp; DevOps*)</t>
+          <t>**STB-601 — Cloud Architecture &amp; DevOps** (*Cloud Architecture &amp; DevOps*)</t>
         </is>
       </c>
     </row>
@@ -39029,7 +39029,7 @@
       </c>
       <c r="B1971" s="7" t="inlineStr">
         <is>
-          <t>**STB-03 — Cybersecurity Risk Management** (*Cybersecurity Risk Management*)</t>
+          <t>**STB-602 — Cybersecurity Risk Management** (*Cybersecurity Risk Management*)</t>
         </is>
       </c>
     </row>
@@ -39711,7 +39711,7 @@
       </c>
       <c r="B2006" s="7" t="inlineStr">
         <is>
-          <t>**STB-04 — IT Governance &amp; Compliance (COBIT 2019)** (*IT Governance &amp; Compliance (COBIT 2019)*)</t>
+          <t>**STB-701 — IT Governance &amp; Compliance (COBIT 2019)** (*IT Governance &amp; Compliance (COBIT 2019)*)</t>
         </is>
       </c>
     </row>
@@ -40393,7 +40393,7 @@
       </c>
       <c r="B2041" s="7" t="inlineStr">
         <is>
-          <t>**STB-05 — IT Service Management (ITIL 4)** (*IT Service Management (ITIL 4)*)</t>
+          <t>**STB-702 — IT Service Management (ITIL 4)** (*IT Service Management (ITIL 4)*)</t>
         </is>
       </c>
     </row>
@@ -41075,7 +41075,7 @@
       </c>
       <c r="B2076" s="7" t="inlineStr">
         <is>
-          <t>**STB-06 — Enterprise Architecture (TOGAF)** (*Enterprise Architecture (TOGAF)*)</t>
+          <t>**STB-703 — Enterprise Architecture (TOGAF)** (*Enterprise Architecture (TOGAF)*)</t>
         </is>
       </c>
     </row>
@@ -41757,7 +41757,7 @@
       </c>
       <c r="B2111" s="7" t="inlineStr">
         <is>
-          <t>**STC-01 — User Experience Research &amp; Design** (*User Experience Research &amp; Design*)</t>
+          <t>**STC-501 — User Experience Research &amp; Design** (*User Experience Research &amp; Design*)</t>
         </is>
       </c>
     </row>
@@ -42439,7 +42439,7 @@
       </c>
       <c r="B2146" s="7" t="inlineStr">
         <is>
-          <t>**STC-02 — Rekayasa &amp; Otomasi Proses Bisnis (BPA)** (*Business Process Automation*)</t>
+          <t>**STC-601 — Rekayasa &amp; Otomasi Proses Bisnis (BPA)** (*Business Process Automation*)</t>
         </is>
       </c>
     </row>
@@ -43121,7 +43121,7 @@
       </c>
       <c r="B2181" s="7" t="inlineStr">
         <is>
-          <t>**STC-03 — Rekayasa Aplikasi Industri Vertikal (FinTech &amp; EdTech)** (*Vertical Industry Application Engineering*)</t>
+          <t>**STC-602 — Rekayasa Aplikasi Industri Vertikal (FinTech &amp; EdTech)** (*Vertical Industry Application Engineering*)</t>
         </is>
       </c>
     </row>
@@ -43803,7 +43803,7 @@
       </c>
       <c r="B2216" s="7" t="inlineStr">
         <is>
-          <t>**STC-04 — Immersive Media &amp; XR Development** (*Immersive Media &amp; XR Development*)</t>
+          <t>**STC-701 — Immersive Media &amp; XR Development** (*Immersive Media &amp; XR Development*)</t>
         </is>
       </c>
     </row>
@@ -44485,7 +44485,7 @@
       </c>
       <c r="B2251" s="7" t="inlineStr">
         <is>
-          <t>**STC-05 — SaaS Architecture &amp; Multi-Tenancy** (*SaaS Architecture &amp; Multi-Tenancy*)</t>
+          <t>**STC-702 — SaaS Architecture &amp; Multi-Tenancy** (*SaaS Architecture &amp; Multi-Tenancy*)</t>
         </is>
       </c>
     </row>
@@ -45167,7 +45167,7 @@
       </c>
       <c r="B2286" s="7" t="inlineStr">
         <is>
-          <t>**STC-06 — Digital Product Management &amp; Agile Practices** (*Digital Product Management &amp; Agile*)</t>
+          <t>**STC-703 — Digital Product Management &amp; Agile Practices** (*Digital Product Management &amp; Agile*)</t>
         </is>
       </c>
     </row>
